--- a/isoReport/docs/listado jira iso.xlsx
+++ b/isoReport/docs/listado jira iso.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://aagricola-my.sharepoint.com/personal/inavarro_atlanticaagricola_com/Documents/Escritorio/Repos/isoReport/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="91" documentId="8_{3196883F-C5CC-444C-8837-DDEB28769FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{53511078-920F-44C8-99A8-FCDE95329BDB}"/>
+  <xr:revisionPtr revIDLastSave="98" documentId="8_{3196883F-C5CC-444C-8837-DDEB28769FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CB66DC7E-62B4-4CB3-8247-82B78A3DC0F3}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{190B92D9-6C2C-4795-950E-F3420A92F605}"/>
   </bookViews>
   <sheets>
     <sheet name="Jira" sheetId="2" r:id="rId1"/>
+    <sheet name="Hoja1" sheetId="3" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="DatosExternos_1" localSheetId="0" hidden="1">Jira!$A$1:$S$126</definedName>
@@ -53,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2269" uniqueCount="758">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2393" uniqueCount="758">
   <si>
     <t>Tipo de Incidencia</t>
   </si>
@@ -2634,7 +2635,13 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{6DAC8D5F-F972-4D80-8E57-29DD8308FB06}" name="Jira" displayName="Jira" ref="A1:S126" tableType="queryTable" totalsRowShown="0">
-  <autoFilter ref="A1:S126" xr:uid="{6DAC8D5F-F972-4D80-8E57-29DD8308FB06}"/>
+  <autoFilter ref="A1:S126" xr:uid="{6DAC8D5F-F972-4D80-8E57-29DD8308FB06}">
+    <filterColumn colId="7">
+      <filters>
+        <filter val="LIBERADO"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <tableColumns count="19">
     <tableColumn id="1" xr3:uid="{3165C56A-AE9B-4ACF-865E-63B15A9104E7}" uniqueName="1" name="Tipo de Incidencia" queryTableFieldId="1" dataDxfId="18"/>
     <tableColumn id="20" xr3:uid="{88F8F6B4-14F1-43CE-9986-DA2F1BC9385B}" uniqueName="20" name="Orden" queryTableFieldId="20" dataDxfId="17"/>
@@ -3056,7 +3063,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>17</v>
       </c>
@@ -3174,7 +3181,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>17</v>
       </c>
@@ -3233,7 +3240,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>17</v>
       </c>
@@ -3292,7 +3299,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -3410,7 +3417,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>17</v>
       </c>
@@ -3469,7 +3476,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>17</v>
       </c>
@@ -3528,7 +3535,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>17</v>
       </c>
@@ -3587,7 +3594,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>17</v>
       </c>
@@ -3705,7 +3712,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>17</v>
       </c>
@@ -3764,7 +3771,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>17</v>
       </c>
@@ -3823,7 +3830,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>17</v>
       </c>
@@ -3882,7 +3889,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>17</v>
       </c>
@@ -3941,7 +3948,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>17</v>
       </c>
@@ -4000,7 +4007,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>17</v>
       </c>
@@ -4059,7 +4066,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>17</v>
       </c>
@@ -4118,7 +4125,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>17</v>
       </c>
@@ -4177,7 +4184,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>17</v>
       </c>
@@ -4236,7 +4243,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>17</v>
       </c>
@@ -4295,7 +4302,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>17</v>
       </c>
@@ -4413,7 +4420,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>17</v>
       </c>
@@ -4472,7 +4479,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>17</v>
       </c>
@@ -4531,7 +4538,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>17</v>
       </c>
@@ -4590,7 +4597,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>17</v>
       </c>
@@ -4649,7 +4656,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>17</v>
       </c>
@@ -4708,7 +4715,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>17</v>
       </c>
@@ -4767,7 +4774,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>17</v>
       </c>
@@ -4885,7 +4892,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>17</v>
       </c>
@@ -4944,7 +4951,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>17</v>
       </c>
@@ -5003,7 +5010,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="35" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>17</v>
       </c>
@@ -5062,7 +5069,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="36" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>17</v>
       </c>
@@ -5121,7 +5128,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="37" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>17</v>
       </c>
@@ -5239,7 +5246,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="39" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>17</v>
       </c>
@@ -5298,7 +5305,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="40" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>17</v>
       </c>
@@ -5416,7 +5423,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="42" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>17</v>
       </c>
@@ -5475,7 +5482,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="43" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>17</v>
       </c>
@@ -5534,7 +5541,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="44" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>17</v>
       </c>
@@ -5593,7 +5600,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="45" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>17</v>
       </c>
@@ -5652,7 +5659,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="46" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>17</v>
       </c>
@@ -5770,7 +5777,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="48" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>17</v>
       </c>
@@ -5829,7 +5836,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="49" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>17</v>
       </c>
@@ -5888,7 +5895,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="50" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>17</v>
       </c>
@@ -6065,7 +6072,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="53" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>17</v>
       </c>
@@ -6242,7 +6249,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="56" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>17</v>
       </c>
@@ -6301,7 +6308,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="57" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>17</v>
       </c>
@@ -6360,7 +6367,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="58" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>17</v>
       </c>
@@ -6537,7 +6544,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="61" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>17</v>
       </c>
@@ -6596,7 +6603,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="62" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>17</v>
       </c>
@@ -6773,7 +6780,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="65" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>17</v>
       </c>
@@ -6832,7 +6839,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="66" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>17</v>
       </c>
@@ -6891,7 +6898,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="67" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>17</v>
       </c>
@@ -6950,7 +6957,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="68" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>17</v>
       </c>
@@ -7068,7 +7075,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="70" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>17</v>
       </c>
@@ -7127,7 +7134,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="71" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>17</v>
       </c>
@@ -7186,7 +7193,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="72" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>17</v>
       </c>
@@ -7245,7 +7252,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="73" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>17</v>
       </c>
@@ -7363,7 +7370,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="75" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>17</v>
       </c>
@@ -7422,7 +7429,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="76" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>17</v>
       </c>
@@ -7481,7 +7488,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="77" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>17</v>
       </c>
@@ -7599,7 +7606,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="79" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>17</v>
       </c>
@@ -7658,7 +7665,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="80" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>17</v>
       </c>
@@ -7717,7 +7724,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="81" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>17</v>
       </c>
@@ -7776,7 +7783,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="82" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>17</v>
       </c>
@@ -7835,7 +7842,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="83" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>17</v>
       </c>
@@ -7894,7 +7901,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="84" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>17</v>
       </c>
@@ -7953,7 +7960,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="85" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>17</v>
       </c>
@@ -8071,7 +8078,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="87" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>17</v>
       </c>
@@ -8130,7 +8137,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="88" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>17</v>
       </c>
@@ -8189,7 +8196,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="89" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>17</v>
       </c>
@@ -8248,7 +8255,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="90" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>17</v>
       </c>
@@ -8484,7 +8491,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="94" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>17</v>
       </c>
@@ -8543,7 +8550,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="95" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>17</v>
       </c>
@@ -8602,7 +8609,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="96" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>17</v>
       </c>
@@ -8661,7 +8668,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="97" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>17</v>
       </c>
@@ -8720,7 +8727,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="98" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>17</v>
       </c>
@@ -8779,7 +8786,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="99" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>17</v>
       </c>
@@ -8897,7 +8904,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="101" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>17</v>
       </c>
@@ -8956,7 +8963,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="102" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>17</v>
       </c>
@@ -9015,7 +9022,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="103" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>17</v>
       </c>
@@ -9074,7 +9081,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="104" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>17</v>
       </c>
@@ -9192,7 +9199,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="106" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>17</v>
       </c>
@@ -9251,7 +9258,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="107" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>17</v>
       </c>
@@ -9310,7 +9317,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="108" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>17</v>
       </c>
@@ -9369,7 +9376,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="109" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>17</v>
       </c>
@@ -9428,7 +9435,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="110" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>17</v>
       </c>
@@ -9605,7 +9612,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="113" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>17</v>
       </c>
@@ -9723,7 +9730,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="115" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>17</v>
       </c>
@@ -9841,7 +9848,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="117" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>17</v>
       </c>
@@ -9900,7 +9907,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="118" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>17</v>
       </c>
@@ -9959,7 +9966,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="119" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>17</v>
       </c>
@@ -10018,7 +10025,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="120" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>17</v>
       </c>
@@ -10077,7 +10084,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="121" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>17</v>
       </c>
@@ -10136,7 +10143,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="122" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>17</v>
       </c>
@@ -10254,7 +10261,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="124" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>17</v>
       </c>
@@ -10313,7 +10320,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="125" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>17</v>
       </c>
@@ -10372,7 +10379,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="126" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>17</v>
       </c>
@@ -10436,6 +10443,455 @@
   <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CFCC4CA-7EEE-4D6B-B657-66991E9FF430}">
+  <dimension ref="A1:D31"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="50.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="31.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.77734375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" t="s">
+        <v>756</v>
+      </c>
+      <c r="D1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>419</v>
+      </c>
+      <c r="B4" t="s">
+        <v>420</v>
+      </c>
+      <c r="C4" t="s">
+        <v>395</v>
+      </c>
+      <c r="D4" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>336</v>
+      </c>
+      <c r="B5" t="s">
+        <v>337</v>
+      </c>
+      <c r="C5" t="s">
+        <v>338</v>
+      </c>
+      <c r="D5" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>650</v>
+      </c>
+      <c r="B6" t="s">
+        <v>651</v>
+      </c>
+      <c r="C6" t="s">
+        <v>652</v>
+      </c>
+      <c r="D6" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>551</v>
+      </c>
+      <c r="B7" t="s">
+        <v>552</v>
+      </c>
+      <c r="C7" t="s">
+        <v>547</v>
+      </c>
+      <c r="D7" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>735</v>
+      </c>
+      <c r="B8" t="s">
+        <v>736</v>
+      </c>
+      <c r="C8" t="s">
+        <v>734</v>
+      </c>
+      <c r="D8" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>499</v>
+      </c>
+      <c r="B9" t="s">
+        <v>500</v>
+      </c>
+      <c r="C9" t="s">
+        <v>494</v>
+      </c>
+      <c r="D9" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>221</v>
+      </c>
+      <c r="B10" t="s">
+        <v>222</v>
+      </c>
+      <c r="C10" t="s">
+        <v>215</v>
+      </c>
+      <c r="D10" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>302</v>
+      </c>
+      <c r="B11" t="s">
+        <v>303</v>
+      </c>
+      <c r="C11" t="s">
+        <v>304</v>
+      </c>
+      <c r="D11" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>95</v>
+      </c>
+      <c r="B12" t="s">
+        <v>96</v>
+      </c>
+      <c r="C12" t="s">
+        <v>97</v>
+      </c>
+      <c r="D12" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>686</v>
+      </c>
+      <c r="B13" t="s">
+        <v>687</v>
+      </c>
+      <c r="C13" t="s">
+        <v>680</v>
+      </c>
+      <c r="D13" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>561</v>
+      </c>
+      <c r="B14" t="s">
+        <v>562</v>
+      </c>
+      <c r="C14" t="s">
+        <v>563</v>
+      </c>
+      <c r="D14" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>621</v>
+      </c>
+      <c r="B15" t="s">
+        <v>622</v>
+      </c>
+      <c r="C15" t="s">
+        <v>593</v>
+      </c>
+      <c r="D15" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>586</v>
+      </c>
+      <c r="B16" t="s">
+        <v>587</v>
+      </c>
+      <c r="C16" t="s">
+        <v>588</v>
+      </c>
+      <c r="D16" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>700</v>
+      </c>
+      <c r="B17" t="s">
+        <v>701</v>
+      </c>
+      <c r="C17" t="s">
+        <v>702</v>
+      </c>
+      <c r="D17" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>429</v>
+      </c>
+      <c r="B18" t="s">
+        <v>430</v>
+      </c>
+      <c r="C18" t="s">
+        <v>431</v>
+      </c>
+      <c r="D18" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>373</v>
+      </c>
+      <c r="B19" t="s">
+        <v>374</v>
+      </c>
+      <c r="C19" t="s">
+        <v>375</v>
+      </c>
+      <c r="D19" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>89</v>
+      </c>
+      <c r="B20" t="s">
+        <v>90</v>
+      </c>
+      <c r="C20" t="s">
+        <v>73</v>
+      </c>
+      <c r="D20" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>423</v>
+      </c>
+      <c r="B21" t="s">
+        <v>424</v>
+      </c>
+      <c r="C21" t="s">
+        <v>425</v>
+      </c>
+      <c r="D21" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>387</v>
+      </c>
+      <c r="B22" t="s">
+        <v>388</v>
+      </c>
+      <c r="C22" t="s">
+        <v>389</v>
+      </c>
+      <c r="D22" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>296</v>
+      </c>
+      <c r="B23" t="s">
+        <v>297</v>
+      </c>
+      <c r="C23" t="s">
+        <v>298</v>
+      </c>
+      <c r="D23" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>721</v>
+      </c>
+      <c r="B24" t="s">
+        <v>722</v>
+      </c>
+      <c r="C24" t="s">
+        <v>707</v>
+      </c>
+      <c r="D24" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>655</v>
+      </c>
+      <c r="B25" t="s">
+        <v>656</v>
+      </c>
+      <c r="C25" t="s">
+        <v>657</v>
+      </c>
+      <c r="D25" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>146</v>
+      </c>
+      <c r="B26" t="s">
+        <v>147</v>
+      </c>
+      <c r="C26" t="s">
+        <v>136</v>
+      </c>
+      <c r="D26" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>434</v>
+      </c>
+      <c r="B27" t="s">
+        <v>435</v>
+      </c>
+      <c r="C27" t="s">
+        <v>436</v>
+      </c>
+      <c r="D27" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>191</v>
+      </c>
+      <c r="B28" t="s">
+        <v>192</v>
+      </c>
+      <c r="C28" t="s">
+        <v>175</v>
+      </c>
+      <c r="D28" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>109</v>
+      </c>
+      <c r="B29" t="s">
+        <v>110</v>
+      </c>
+      <c r="C29" t="s">
+        <v>111</v>
+      </c>
+      <c r="D29" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>196</v>
+      </c>
+      <c r="B30" t="s">
+        <v>197</v>
+      </c>
+      <c r="C30" t="s">
+        <v>198</v>
+      </c>
+      <c r="D30" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>134</v>
+      </c>
+      <c r="B31" t="s">
+        <v>135</v>
+      </c>
+      <c r="C31" t="s">
+        <v>136</v>
+      </c>
+      <c r="D31" t="s">
+        <v>47</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
